--- a/projects/demo/cases.xlsx
+++ b/projects/demo/cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,72 +413,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>用例ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>标题</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>step_no</t>
+          <t>步骤描述</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>期望结果</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tags</t>
+          <t>标签</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tc001</t>
+          <t>TC001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>访问示例页</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+          <t>登录成功</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>打开登录页，输入 tomsmith / SuperSecretPassword!，点击登录</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>go</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://example.com</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+          <t>显示 Secure Area</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>smoke</t>
         </is>
@@ -487,33 +473,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tc001</t>
+          <t>TC002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>断言标题</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
+          <t>登录失败</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>打开登录页，输入错误密码，点击登录</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>assert_text</t>
+          <t>显示错误提示</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Example Domain</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
